--- a/data/s0/Kanaleneiland/archetypes/pop_archetypes_family.xlsx
+++ b/data/s0/Kanaleneiland/archetypes/pop_archetypes_family.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\asier.divasson\Documents\GitHub\CogniCity\Archetypes\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\asier.divasson\Documents\GitHub\CogniCity\data\s0\Kanaleneiland\archetypes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB789C15-FAF9-467B-9D03-5044B38B6A18}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCCCFDE5-B06D-488B-BA26-F86E32B0A0EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="855" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -19,6 +19,20 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -121,12 +135,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -141,9 +161,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="1" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -472,8 +493,8 @@
       <c r="B2" t="s">
         <v>11</v>
       </c>
-      <c r="C2">
-        <v>20</v>
+      <c r="C2" s="2">
+        <v>4755</v>
       </c>
       <c r="D2" t="s">
         <v>9</v>
@@ -498,8 +519,9 @@
       <c r="B3" t="s">
         <v>4</v>
       </c>
-      <c r="C3">
-        <v>40</v>
+      <c r="C3" s="2">
+        <f>2315*(18175/(18175+14270))*(684844/(684844+291411))</f>
+        <v>909.71639235852888</v>
       </c>
       <c r="D3" t="s">
         <v>9</v>
@@ -521,8 +543,9 @@
       <c r="B4" t="s">
         <v>5</v>
       </c>
-      <c r="C4">
-        <v>2</v>
+      <c r="C4" s="2">
+        <f>2315*(14270/(18175+14270))*0.5</f>
+        <v>509.093080597935</v>
       </c>
       <c r="D4" t="s">
         <v>9</v>
@@ -541,8 +564,9 @@
       <c r="B5" t="s">
         <v>6</v>
       </c>
-      <c r="C5">
-        <v>2</v>
+      <c r="C5" s="2">
+        <f>2315*(14270/(18175+14270))*0.5</f>
+        <v>509.093080597935</v>
       </c>
       <c r="D5" t="s">
         <v>9</v>
@@ -561,8 +585,9 @@
       <c r="B6" t="s">
         <v>13</v>
       </c>
-      <c r="C6">
-        <v>6</v>
+      <c r="C6" s="2">
+        <f>1795*(1740/(52620+1740))</f>
+        <v>57.455849889624716</v>
       </c>
       <c r="D6" t="s">
         <v>9</v>
@@ -578,8 +603,9 @@
       <c r="B7" t="s">
         <v>7</v>
       </c>
-      <c r="C7">
-        <v>15</v>
+      <c r="C7" s="2">
+        <f>1795*(52620/(52620+1740))*(88115/209920)</f>
+        <v>729.34309635563875</v>
       </c>
       <c r="D7" t="s">
         <v>9</v>
@@ -595,8 +621,9 @@
       <c r="B8" t="s">
         <v>8</v>
       </c>
-      <c r="C8">
-        <v>5</v>
+      <c r="C8" s="2">
+        <f>2315*(18175/(18175+14270))*((291411/(684844+291411)))</f>
+        <v>387.09744644560118</v>
       </c>
       <c r="D8" t="s">
         <v>9</v>
@@ -618,8 +645,9 @@
       <c r="B9" t="s">
         <v>10</v>
       </c>
-      <c r="C9">
-        <v>10</v>
+      <c r="C9" s="2">
+        <f>1795*(52620/(52620+1740))*(1-(88115/209920))</f>
+        <v>1008.2010537547363</v>
       </c>
       <c r="D9" t="s">
         <v>9</v>
